--- a/AAII_Financials/Yearly/NE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NE_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>NE</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2589000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1413800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>847800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>964300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1305400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1082800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1236900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2302100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3352300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>2538100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2200700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2695800</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1543900</v>
+      </c>
+      <c r="E9" s="3">
         <v>961500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>745000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>615700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>747400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>667000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>661400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>923200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1302800</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>1230800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1047700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1476500</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1045100</v>
+      </c>
+      <c r="E10" s="3">
         <v>452300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>102800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>348600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>558000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>415800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>575500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1378900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2049400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>1307400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1153000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1219300</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E14" s="3">
         <v>93600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-203900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3936500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>584700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>803900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>121600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1440900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>418300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-9300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-12900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-21200</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E15" s="3">
         <v>146900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>110200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>374100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>440200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>486500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>548000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>611100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>634300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>511500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>440300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>658600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2040700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1194000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>533500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5047500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1941100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2030700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1402600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3044400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2432300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>1797600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1575100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2205300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>548300</v>
+      </c>
+      <c r="E18" s="3">
         <v>219900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>314300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4083200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-635700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-947900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-165700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-742400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>920000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>740500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>625600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>490500</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E20" s="3">
         <v>14400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>73600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>36300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>4200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>872700</v>
+      </c>
+      <c r="E21" s="3">
         <v>381100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>549700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3700100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-189400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-453000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>390200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-133000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>1624100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1387700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1150600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E22" s="3">
         <v>42700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>32000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>164700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>279400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>297600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>292000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>222900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>213900</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>106300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>85800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>55700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>512200</v>
+      </c>
+      <c r="E23" s="3">
         <v>191500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>356000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4238900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-909100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1237200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-449800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-967000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>742400</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>638400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>543400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>436300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E24" s="3">
         <v>22600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-221400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-38500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-106600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>151600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-109200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>159200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>92100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>95200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>72600</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>481900</v>
+      </c>
+      <c r="E26" s="3">
         <v>168900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>352200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4017500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-870500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1130500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-601400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-857900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>583200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>546300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>448200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>363600</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>481900</v>
+      </c>
+      <c r="E27" s="3">
         <v>168900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>352200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4017500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-696800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-885100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-624000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-929600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500100</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>469300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>409100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>367200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,51 +1582,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>39000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-3800</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>107500</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
         <v>304100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>108000</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-73600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-36300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>-4200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>481900</v>
+      </c>
+      <c r="E33" s="3">
         <v>168900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>352200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3978500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-885100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-516500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-929600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>773400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>517000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>367200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>481900</v>
+      </c>
+      <c r="E35" s="3">
         <v>168900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>352200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3978500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-885100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-516500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-929600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>773400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>517000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>367200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>360800</v>
+      </c>
+      <c r="E41" s="3">
         <v>476200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>194100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>343300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>104600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>375200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>662800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>725700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>512200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3">
         <v>114500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>282100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>239200</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1986,51 +2075,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>592900</v>
+      </c>
+      <c r="E43" s="3">
         <v>514100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>222200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>189300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>279700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>221200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>310000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>374600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>554500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>1089300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>856100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>662400</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,111 +2165,120 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>108100</v>
+      </c>
+      <c r="E45" s="3">
         <v>61500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>69600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>62600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>66100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>92300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>173900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>187100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>167100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>158000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1061700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1051800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>455600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>602300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>422100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>659100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1039000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1192600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1240600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" s="3">
         <v>1390900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1305300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1059600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>200</v>
+      </c>
+      <c r="E47" s="3">
         <v>400</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>3200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9500</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2184,75 +2288,81 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4148900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4015900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1495800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3603700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7767400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8480700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9489200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10061900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11483600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>14558100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13026000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12130300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E49" s="3">
         <v>60400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>61800</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2268,8 +2378,8 @@
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2280,9 +2390,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>286500</v>
+      </c>
+      <c r="E52" s="3">
         <v>106500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>60200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>54800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>85500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>125100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>266400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>185600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>141400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>268900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>276500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>305200</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5507400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5234900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2073400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4263900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8284500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9264900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10794700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11440100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12865600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" s="3">
         <v>16218000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14607800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13495200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,79 +2656,83 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>395200</v>
+      </c>
+      <c r="E57" s="3">
         <v>290700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>120400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>95200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>108200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>125600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>108200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>223200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>347200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>350100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>436000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>159700</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>62500</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>249800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>299900</v>
       </c>
       <c r="K58" s="3">
         <v>299900</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
+      <c r="L58" s="3">
+        <v>299900</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -2607,180 +2740,195 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>246500</v>
+      </c>
+      <c r="E59" s="3">
         <v>216700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>128000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>123200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>346200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>239900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>259100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>225200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>340400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>704700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>561300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>515100</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>641700</v>
+      </c>
+      <c r="E60" s="3">
         <v>667100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>248400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>218400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>516900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>365500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>593000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>633300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>863600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" s="3">
         <v>1051900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>911400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>827200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>586200</v>
+      </c>
+      <c r="E61" s="3">
         <v>513100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>216000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3997900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3779500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3877400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3795900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4040200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4162600</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>5556300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4634400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4072000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>358300</v>
+      </c>
+      <c r="E62" s="3">
         <v>447600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>108400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>359000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>329100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>367500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>455100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>299100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>417200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>559800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>573700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>548300</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1586200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1627800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>572800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4575300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4625500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5011800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5518500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5681400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6166400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="3">
         <v>7895400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6884600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6088600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>541200</v>
+      </c>
+      <c r="E72" s="3">
         <v>255900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>102000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1070700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2907800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3608400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4637700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5154200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6131500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>7591900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7066000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6676400</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3921200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3607100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1500600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-311400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3659000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4253200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5276200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5758700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6699200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N76" s="3">
         <v>8322600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7723200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7406500</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>481900</v>
+      </c>
+      <c r="E81" s="3">
         <v>168900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>352200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3978500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-885100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-516500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-929600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>773400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>517000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>367200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E83" s="3">
         <v>146900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>161700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>374100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>440200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>486500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>548000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>611100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>634300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>879400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>758600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>658600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>574300</v>
+      </c>
+      <c r="E89" s="3">
         <v>281000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>273200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>186800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>171900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>416700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1142700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1764900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3">
         <v>1702300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1381700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>740200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-409600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-174300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-169000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-148900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-268800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-194800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-120700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-711400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-422500</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2487500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1669800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2621200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-366500</v>
+      </c>
+      <c r="E94" s="3">
         <v>375800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>193400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-121500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-256000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-189400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-118300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-686600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-432500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-2485100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1790900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2521500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,13 +4222,14 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-98800</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4014,26 +4247,29 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-47500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-315500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-194900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-138300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-150500</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,51 +4399,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-325800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-367800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-367900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>107400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-269400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-361200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-242700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-888600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>615200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>452100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1682600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4241,49 +4489,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="E102" s="3">
         <v>289000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-168300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>259100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-270000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-286900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-62900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>213500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>443700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N102" s="3">
         <v>-167600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>42900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-98700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>NE</t>
   </si>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2589000</v>
+        <v>2461700</v>
       </c>
       <c r="E8" s="3">
-        <v>1413800</v>
+        <v>1332800</v>
       </c>
       <c r="F8" s="3">
-        <v>847800</v>
+        <v>782200</v>
       </c>
       <c r="G8" s="3">
-        <v>964300</v>
+        <v>909200</v>
       </c>
       <c r="H8" s="3">
-        <v>1305400</v>
+        <v>1246100</v>
       </c>
       <c r="I8" s="3">
-        <v>1082800</v>
+        <v>1036100</v>
       </c>
       <c r="J8" s="3">
-        <v>1236900</v>
+        <v>1207000</v>
       </c>
       <c r="K8" s="3">
         <v>2302100</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1543900</v>
+        <v>1452300</v>
       </c>
       <c r="E9" s="3">
-        <v>961500</v>
+        <v>897100</v>
       </c>
       <c r="F9" s="3">
-        <v>745000</v>
+        <v>686400</v>
       </c>
       <c r="G9" s="3">
-        <v>615700</v>
+        <v>567500</v>
       </c>
       <c r="H9" s="3">
-        <v>747400</v>
+        <v>698300</v>
       </c>
       <c r="I9" s="3">
-        <v>667000</v>
+        <v>629900</v>
       </c>
       <c r="J9" s="3">
-        <v>661400</v>
+        <v>628600</v>
       </c>
       <c r="K9" s="3">
         <v>923200</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1045100</v>
+        <v>1009400</v>
       </c>
       <c r="E10" s="3">
-        <v>452300</v>
+        <v>435700</v>
       </c>
       <c r="F10" s="3">
-        <v>102800</v>
+        <v>95800</v>
       </c>
       <c r="G10" s="3">
-        <v>348600</v>
+        <v>341700</v>
       </c>
       <c r="H10" s="3">
-        <v>558000</v>
+        <v>547700</v>
       </c>
       <c r="I10" s="3">
-        <v>415800</v>
+        <v>406100</v>
       </c>
       <c r="J10" s="3">
-        <v>575500</v>
+        <v>578400</v>
       </c>
       <c r="K10" s="3">
         <v>1378900</v>
@@ -972,13 +972,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>67000</v>
+        <v>62000</v>
       </c>
       <c r="E14" s="3">
-        <v>93600</v>
+        <v>3400</v>
       </c>
       <c r="F14" s="3">
-        <v>-203900</v>
+        <v>-452100</v>
       </c>
       <c r="G14" s="3">
         <v>3936500</v>
@@ -990,7 +990,7 @@
         <v>803900</v>
       </c>
       <c r="J14" s="3">
-        <v>121600</v>
+        <v>135900</v>
       </c>
       <c r="K14" s="3">
         <v>1440900</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2040700</v>
+        <v>1846400</v>
       </c>
       <c r="E17" s="3">
-        <v>1194000</v>
+        <v>1109600</v>
       </c>
       <c r="F17" s="3">
-        <v>533500</v>
+        <v>857700</v>
       </c>
       <c r="G17" s="3">
-        <v>5047500</v>
+        <v>1055100</v>
       </c>
       <c r="H17" s="3">
-        <v>1941100</v>
+        <v>1297500</v>
       </c>
       <c r="I17" s="3">
-        <v>2030700</v>
+        <v>1177100</v>
       </c>
       <c r="J17" s="3">
-        <v>1402600</v>
+        <v>1234400</v>
       </c>
       <c r="K17" s="3">
         <v>3044400</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>548300</v>
+        <v>615300</v>
       </c>
       <c r="E18" s="3">
-        <v>219900</v>
+        <v>223300</v>
       </c>
       <c r="F18" s="3">
-        <v>314300</v>
+        <v>-75500</v>
       </c>
       <c r="G18" s="3">
-        <v>-4083200</v>
+        <v>-145900</v>
       </c>
       <c r="H18" s="3">
-        <v>-635700</v>
+        <v>-51500</v>
       </c>
       <c r="I18" s="3">
-        <v>-947900</v>
+        <v>-141000</v>
       </c>
       <c r="J18" s="3">
-        <v>-165700</v>
+        <v>-27300</v>
       </c>
       <c r="K18" s="3">
         <v>-742400</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>23100</v>
+        <v>-18100</v>
       </c>
       <c r="E20" s="3">
-        <v>14400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>73600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>9000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>8300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>7900</v>
+        <v>-14400</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>-1700</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>872700</v>
+        <v>934800</v>
       </c>
       <c r="E21" s="3">
-        <v>381100</v>
+        <v>384500</v>
       </c>
       <c r="F21" s="3">
-        <v>549700</v>
+        <v>34600</v>
       </c>
       <c r="G21" s="3">
-        <v>-3700100</v>
+        <v>228200</v>
       </c>
       <c r="H21" s="3">
-        <v>-189400</v>
+        <v>388800</v>
       </c>
       <c r="I21" s="3">
-        <v>-453000</v>
+        <v>345600</v>
       </c>
       <c r="J21" s="3">
-        <v>390200</v>
+        <v>520700</v>
       </c>
       <c r="K21" s="3">
         <v>-133000</v>
@@ -1376,7 +1376,7 @@
         <v>3800</v>
       </c>
       <c r="G24" s="3">
-        <v>-221400</v>
+        <v>-260400</v>
       </c>
       <c r="H24" s="3">
         <v>-38500</v>
@@ -1385,7 +1385,7 @@
         <v>-106600</v>
       </c>
       <c r="J24" s="3">
-        <v>151600</v>
+        <v>42600</v>
       </c>
       <c r="K24" s="3">
         <v>-109200</v>
@@ -1466,7 +1466,7 @@
         <v>352200</v>
       </c>
       <c r="G26" s="3">
-        <v>-4017500</v>
+        <v>-3978500</v>
       </c>
       <c r="H26" s="3">
         <v>-870500</v>
@@ -1475,7 +1475,7 @@
         <v>-1130500</v>
       </c>
       <c r="J26" s="3">
-        <v>-601400</v>
+        <v>-492400</v>
       </c>
       <c r="K26" s="3">
         <v>-857900</v>
@@ -1511,16 +1511,16 @@
         <v>352200</v>
       </c>
       <c r="G27" s="3">
-        <v>-4017500</v>
+        <v>-3978500</v>
       </c>
       <c r="H27" s="3">
-        <v>-696800</v>
+        <v>-700600</v>
       </c>
       <c r="I27" s="3">
-        <v>-885100</v>
+        <v>-885000</v>
       </c>
       <c r="J27" s="3">
-        <v>-624000</v>
+        <v>-516500</v>
       </c>
       <c r="K27" s="3">
         <v>-929600</v>
@@ -1591,17 +1591,17 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>-3800</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>107500</v>
+        <v>-1500</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-23100</v>
+        <v>18100</v>
       </c>
       <c r="E32" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-73600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-7900</v>
+        <v>14400</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>1700</v>
@@ -2010,7 +2010,7 @@
         <v>104600</v>
       </c>
       <c r="I41" s="3">
-        <v>375200</v>
+        <v>375900</v>
       </c>
       <c r="J41" s="3">
         <v>662800</v>
@@ -2103,7 +2103,7 @@
         <v>221200</v>
       </c>
       <c r="J43" s="3">
-        <v>310000</v>
+        <v>331300</v>
       </c>
       <c r="K43" s="3">
         <v>374600</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,26 +2174,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>108100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>61500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>39300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>69600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>37800</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I45" s="3">
-        <v>62600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>66100</v>
+        <v>47000</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>92300</v>
@@ -2264,20 +2264,20 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>400</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>9500</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -2325,7 +2325,7 @@
         <v>7767400</v>
       </c>
       <c r="I48" s="3">
-        <v>8480700</v>
+        <v>4023500</v>
       </c>
       <c r="J48" s="3">
         <v>9489200</v>
@@ -2363,17 +2363,17 @@
       <c r="F49" s="3">
         <v>61800</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
@@ -2504,11 +2504,11 @@
       <c r="H52" s="3">
         <v>85500</v>
       </c>
-      <c r="I52" s="3">
-        <v>125100</v>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J52" s="3">
-        <v>266400</v>
+        <v>231900</v>
       </c>
       <c r="K52" s="3">
         <v>185600</v>
@@ -2595,7 +2595,7 @@
         <v>8284500</v>
       </c>
       <c r="I54" s="3">
-        <v>9264900</v>
+        <v>4916400</v>
       </c>
       <c r="J54" s="3">
         <v>10794700</v>
@@ -2708,19 +2708,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>10600</v>
       </c>
       <c r="E58" s="3">
-        <v>159700</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
+        <v>183500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H58" s="3">
-        <v>62500</v>
+        <v>69100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>246500</v>
+        <v>127800</v>
       </c>
       <c r="E59" s="3">
-        <v>216700</v>
+        <v>107000</v>
       </c>
       <c r="F59" s="3">
-        <v>128000</v>
+        <v>51100</v>
       </c>
       <c r="G59" s="3">
-        <v>123200</v>
+        <v>76500</v>
       </c>
       <c r="H59" s="3">
-        <v>346200</v>
+        <v>165100</v>
       </c>
       <c r="I59" s="3">
-        <v>239900</v>
+        <v>87200</v>
       </c>
       <c r="J59" s="3">
-        <v>259100</v>
+        <v>81700</v>
       </c>
       <c r="K59" s="3">
         <v>225200</v>
@@ -2813,7 +2813,7 @@
         <v>516900</v>
       </c>
       <c r="I60" s="3">
-        <v>365500</v>
+        <v>364000</v>
       </c>
       <c r="J60" s="3">
         <v>593000</v>
@@ -2843,19 +2843,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>586200</v>
+        <v>601300</v>
       </c>
       <c r="E61" s="3">
-        <v>513100</v>
+        <v>536900</v>
       </c>
       <c r="F61" s="3">
-        <v>216000</v>
+        <v>229200</v>
       </c>
       <c r="G61" s="3">
-        <v>3997900</v>
+        <v>3988900</v>
       </c>
       <c r="H61" s="3">
-        <v>3779500</v>
+        <v>3806300</v>
       </c>
       <c r="I61" s="3">
         <v>3877400</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>358300</v>
+        <v>251100</v>
       </c>
       <c r="E62" s="3">
-        <v>447600</v>
+        <v>207800</v>
       </c>
       <c r="F62" s="3">
-        <v>108400</v>
+        <v>55100</v>
       </c>
       <c r="G62" s="3">
-        <v>359000</v>
+        <v>298300</v>
       </c>
       <c r="H62" s="3">
-        <v>329100</v>
+        <v>159700</v>
       </c>
       <c r="I62" s="3">
-        <v>367500</v>
+        <v>251400</v>
       </c>
       <c r="J62" s="3">
-        <v>455100</v>
+        <v>173100</v>
       </c>
       <c r="K62" s="3">
         <v>299100</v>
@@ -3083,10 +3083,10 @@
         <v>4625500</v>
       </c>
       <c r="I66" s="3">
-        <v>5011800</v>
+        <v>4537900</v>
       </c>
       <c r="J66" s="3">
-        <v>5518500</v>
+        <v>4844000</v>
       </c>
       <c r="K66" s="3">
         <v>5681400</v>
@@ -3327,7 +3327,7 @@
         <v>2907800</v>
       </c>
       <c r="I72" s="3">
-        <v>3608400</v>
+        <v>-469500</v>
       </c>
       <c r="J72" s="3">
         <v>4637700</v>
@@ -3507,7 +3507,7 @@
         <v>3659000</v>
       </c>
       <c r="I76" s="3">
-        <v>4253200</v>
+        <v>201400</v>
       </c>
       <c r="J76" s="3">
         <v>5276200</v>
@@ -3702,7 +3702,7 @@
         <v>146900</v>
       </c>
       <c r="F83" s="3">
-        <v>161700</v>
+        <v>110200</v>
       </c>
       <c r="G83" s="3">
         <v>374100</v>
@@ -4229,7 +4229,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-98800</v>
+        <v>98800</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4453,26 +4453,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/NE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
   <si>
     <t>NE</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2918800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2461700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1332800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>782200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>909200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1246100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1036100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1207000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2302100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3352300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>2538100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2200700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2695800</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1687200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1452300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>897100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>686400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>567500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>698300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>629900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>628600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>923200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1302800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>1230800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1047700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1476500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1231600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1009400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>435700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>95800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>341700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>547700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>406100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>578400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1378900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2049400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>1307400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1153000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1219300</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E14" s="3">
         <v>62000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-452100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3936500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>584700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>803900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>135900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1440900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>418300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-9300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-12900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>428600</v>
+      </c>
+      <c r="E15" s="3">
         <v>301300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>146900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>110200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>374100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>440200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>486500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>548000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>611100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>634300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="3">
         <v>511500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>440300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>658600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2222700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1846400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1109600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>857700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1055100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1297500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1177100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1234400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3044400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2432300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>1797600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1575100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2205300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>696100</v>
+      </c>
+      <c r="E18" s="3">
         <v>615300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>223300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-75500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-145900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-51500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-141000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-742400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>920000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>740500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>625600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>490500</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,17 +1213,18 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-14400</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1207,207 +1240,222 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>36300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>4200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1107200</v>
+      </c>
+      <c r="E21" s="3">
         <v>934800</v>
       </c>
-      <c r="E21" s="3">
-        <v>384500</v>
-      </c>
       <c r="F21" s="3">
+        <v>370100</v>
+      </c>
+      <c r="G21" s="3">
         <v>34600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>228200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>388800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>345600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>520700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-133000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>1624100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1387700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1150600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E22" s="3">
         <v>59100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>32000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>164700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>279400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>297600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>292000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>222900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>213900</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>106300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>85800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>55700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>492300</v>
+      </c>
+      <c r="E23" s="3">
         <v>512200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>191500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>356000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4238900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-909100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1237200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-449800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-967000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>742400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>638400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>543400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>436300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E24" s="3">
         <v>30300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-260400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-38500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-106600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>42600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-109200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>159200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>92100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>95200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>72600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E26" s="3">
         <v>481900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>168900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>352200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3978500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-870500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1130500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-492400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-857900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>583200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>546300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>448200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>363600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E27" s="3">
         <v>481900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>168900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>352200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3978500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-700600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-885000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-516500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-929600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>469300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>409100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>367200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1604,35 +1664,38 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-3800</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1500</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>304100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>108000</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,18 +1786,21 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E32" s="3">
         <v>18100</v>
       </c>
-      <c r="E32" s="3">
-        <v>14400</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
@@ -1747,72 +1816,78 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-36300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>-4200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E33" s="3">
         <v>481900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>168900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>352200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3978500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-700600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-885100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-516500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-929600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>773400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>517000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>367200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E35" s="3">
         <v>481900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>168900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>352200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3978500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-700600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-885100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-516500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-929600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>773400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>517000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>367200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="N38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>247300</v>
+      </c>
+      <c r="E41" s="3">
         <v>360800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>476200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>194100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>343300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>104600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>375900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>662800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>725700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>512200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O41" s="3">
         <v>114500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>282100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>239200</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2078,54 +2167,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>879400</v>
+      </c>
+      <c r="E43" s="3">
         <v>592900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>514100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>222200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>189300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>279700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>221200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>331300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>374600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>554500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O43" s="3">
         <v>1089300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>856100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>662400</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,9 +2263,12 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2189,78 +2287,84 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>47000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>92300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>173900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>187100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>167100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>158000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1388900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1061700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1051800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>455600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>602300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>422100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>659100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1039000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1192600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1240600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O46" s="3">
         <v>1390900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1305300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1059600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2291,81 +2395,87 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6149200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4148900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4015900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1495800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3603700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7767400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4023500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9489200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>10061900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11483600</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O48" s="3">
         <v>14558100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13026000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12130300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>200</v>
+      </c>
+      <c r="E49" s="3">
         <v>10100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>60400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>61800</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -2375,14 +2485,14 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2393,9 +2503,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>415500</v>
+      </c>
+      <c r="E52" s="3">
         <v>286500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>106500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>60200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>54800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>85500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>231900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>185600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>141400</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O52" s="3">
         <v>268900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>276500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>305200</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7964800</v>
+      </c>
+      <c r="E54" s="3">
         <v>5507400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5234900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2073400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4263900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8284500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4916400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10794700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11440100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12865600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O54" s="3">
         <v>16218000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14607800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13495200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,85 +2786,89 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>397600</v>
+      </c>
+      <c r="E57" s="3">
         <v>395200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>290700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>95200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>108200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>125600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>84000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>108200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>223200</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>347200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>350100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>436000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E58" s="3">
         <v>10600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>183500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>249800</v>
-      </c>
-      <c r="K58" s="3">
-        <v>299900</v>
       </c>
       <c r="L58" s="3">
         <v>299900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>299900</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -2743,192 +2876,207 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>352200</v>
+      </c>
+      <c r="E59" s="3">
         <v>127800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>107000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>76500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>165100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>87200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>225200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>340400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>704700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>561300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>515100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>940400</v>
+      </c>
+      <c r="E60" s="3">
         <v>641700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>667100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>248400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>218400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>516900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>364000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>593000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>633300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>863600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O60" s="3">
         <v>1051900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>911400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>827200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2057400</v>
+      </c>
+      <c r="E61" s="3">
         <v>601300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>536900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>229200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3988900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3806300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3877400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3795900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4040200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4162600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>5556300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4634400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4072000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>254400</v>
+      </c>
+      <c r="E62" s="3">
         <v>251100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>207800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>55100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>298300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>159700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>251400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>173100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>299100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>417200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>559800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>573700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>548300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3313400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1586200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1627800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>572800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4575300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4625500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4537900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4844000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5681400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6166400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O66" s="3">
         <v>7895400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6884600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6088600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>411200</v>
+      </c>
+      <c r="E72" s="3">
         <v>541200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>255900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>102000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1070700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2907800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-469500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4637700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5154200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6131500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3">
         <v>7591900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7066000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6676400</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4651400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3921200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3607100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1500600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-311400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3659000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>201400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5276200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5758700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6699200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O76" s="3">
         <v>8322600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7723200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7406500</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N80" s="2">
+      <c r="N80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>448400</v>
+      </c>
+      <c r="E81" s="3">
         <v>481900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>168900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>352200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3978500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-700600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-885100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-516500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-929600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>773400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>517000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>367200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>428600</v>
+      </c>
+      <c r="E83" s="3">
         <v>301300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>146900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>110200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>374100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>440200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>486500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>548000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>611100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>634300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>879400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>758600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>658600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>655500</v>
+      </c>
+      <c r="E89" s="3">
         <v>574300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>281000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>273200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>186800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>171900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>416700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1142700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1764900</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>1702300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1381700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>740200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-575300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-409600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-174300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-169000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-148900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-268800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-194800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-120700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-711400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-422500</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3">
         <v>-2487500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1669800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2621200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-959000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-366500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>375800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>193400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-121500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-256000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-189400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-118300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-686600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-432500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-2485100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1790900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2521500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,17 +4455,18 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>277800</v>
+      </c>
+      <c r="E96" s="3">
         <v>98800</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -4250,26 +4483,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-47500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-315500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-194900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-138300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-150500</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,54 +4644,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>188100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-325800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-367800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-367900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>107400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-269400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-361200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-242700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-888600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>615200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>452100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1682600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4474,8 +4722,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4492,52 +4740,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-118000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>289000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-168300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>259100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-270000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-286900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-62900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>213500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>443700</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O102" s="3">
         <v>-167600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>42900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-98700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
   <si>
     <t>NE</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3107200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2918800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2461700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1332800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>782200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>909200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1246100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1036100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1207000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2302100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3352300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>2538100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2200700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2695800</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1951200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1687200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1452300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>897100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>686400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>567500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>698300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>629900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>628600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>923200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1302800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>1230800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1047700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1476500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1156100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1231600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1009400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>435700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>95800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>341700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>547700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>406100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>578400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1378900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2049400</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>1307400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1153000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1219300</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E14" s="3">
         <v>92100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>62000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-452100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3936500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>584700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>803900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>135900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1440900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>418300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-9300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-21200</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>585500</v>
+      </c>
+      <c r="E15" s="3">
         <v>428600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>301300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>146900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>110200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>374100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>440200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>486500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>548000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>611100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>634300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>511500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>440300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>658600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2627800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2222700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1846400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1109600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>857700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1055100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1297500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1177100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1234400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3044400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2432300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>1797600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1575100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2205300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>479400</v>
+      </c>
+      <c r="E18" s="3">
         <v>696100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>615300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>223300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-75500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-145900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-51500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-141000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-742400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>920000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>740500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>625600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>490500</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,20 +1246,21 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E20" s="3">
         <v>17400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18100</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1243,219 +1276,234 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>36300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>4200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1073300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1107200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>934800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>370100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>34600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>228200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>388800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>345600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>520700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-133000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>1624100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1387700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1150600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E22" s="3">
         <v>94200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>59100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>32000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>164700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>279400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>297600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>292000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>222900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>213900</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>106300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>85800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>55700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>273100</v>
+      </c>
+      <c r="E23" s="3">
         <v>492300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>512200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>191500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>356000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4238900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-909100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1237200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-449800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-967000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>742400</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>638400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>543400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>436300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E24" s="3">
         <v>44000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-260400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-38500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-106600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-109200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>159200</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>92100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>95200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>72600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E26" s="3">
         <v>448400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>481900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>168900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>352200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3978500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-870500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1130500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-492400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-857900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>583200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>546300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>448200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>363600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E27" s="3">
         <v>448400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>481900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>168900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>352200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3978500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-885000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-516500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-929600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>469300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>409100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>367200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1667,35 +1727,38 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-3800</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1500</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3">
         <v>304100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>108000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,21 +1855,24 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18100</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
@@ -1819,75 +1888,81 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-36300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>-4200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E33" s="3">
         <v>448400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>481900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>168900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>352200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3978500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-885100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-516500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-929600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>773400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>517000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>367200</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E35" s="3">
         <v>448400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>481900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>168900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>352200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3978500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-885100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-516500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-929600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>773400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>517000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>367200</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>471400</v>
+      </c>
+      <c r="E41" s="3">
         <v>247300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>360800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>476200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>194100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>343300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>104600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>375900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>662800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>725700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>512200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P41" s="3">
         <v>114500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>282100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>239200</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2170,57 +2259,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>697900</v>
+      </c>
+      <c r="E43" s="3">
         <v>879400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>592900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>514100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>222200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>189300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>279700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>221200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>331300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>374600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>554500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P43" s="3">
         <v>1089300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>856100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>662400</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,9 +2361,12 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2290,81 +2388,87 @@
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>47000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>92300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>173900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>187100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>167100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>158000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1272300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1388900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1061700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1051800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>455600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>602300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>422100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>659100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1039000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1192600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1240600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P46" s="3">
         <v>1390900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1305300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1059600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2398,87 +2502,93 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5562600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6149200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4148900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4015900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1495800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3603700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7767400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4023500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9489200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10061900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11483600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P48" s="3">
         <v>14558100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13026000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12130300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>10100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>60400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>61800</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -2488,14 +2598,14 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2506,9 +2616,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>415500</v>
+        <v>693800</v>
       </c>
       <c r="E52" s="3">
+        <v>415700</v>
+      </c>
+      <c r="F52" s="3">
         <v>286500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>106500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>60200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>85500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>231900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>185600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>141400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>268900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>276500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>305200</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7529800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7964800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5507400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5234900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2073400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4263900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8284500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4916400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10794700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11440100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12865600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P54" s="3">
         <v>16218000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14607800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13495200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,91 +2916,95 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>298800</v>
+      </c>
+      <c r="E57" s="3">
         <v>397600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>395200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>290700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>95200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>108200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>125600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>84000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>108200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>223200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P57" s="3">
         <v>347200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>350100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>436000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E58" s="3">
         <v>37600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>183500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>69100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>249800</v>
-      </c>
-      <c r="L58" s="3">
-        <v>299900</v>
       </c>
       <c r="M58" s="3">
         <v>299900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
+      <c r="N58" s="3">
+        <v>299900</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -2879,204 +3012,219 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E59" s="3">
         <v>352200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>127800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>107000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>51100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>76500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>165100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>87200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>225200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>340400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>704700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>561300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>515100</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>759700</v>
+      </c>
+      <c r="E60" s="3">
         <v>940400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>641700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>667100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>248400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>218400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>516900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>364000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>593000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>633300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>863600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P60" s="3">
         <v>1051900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>911400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>827200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2027700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2057400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>601300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>536900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>229200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3988900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3806300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3877400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3795900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4040200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4162600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>5556300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4634400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4072000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E62" s="3">
         <v>254400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>251100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>207800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>55100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>298300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>159700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>251400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>173100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>299100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>417200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3">
         <v>559800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>573700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>548300</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2980900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3313400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1586200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1627800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>572800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4575300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4625500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4537900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4844000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5681400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6166400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P66" s="3">
         <v>7895400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6884600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6088600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>286600</v>
+      </c>
+      <c r="E72" s="3">
         <v>411200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>541200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>255900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>102000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1070700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2907800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-469500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4637700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5154200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6131500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>7591900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7066000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6676400</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4548900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4651400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3921200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3607100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1500600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-311400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3659000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>201400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5276200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5758700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6699200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P76" s="3">
         <v>8322600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7723200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7406500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O80" s="2">
+      <c r="O80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E81" s="3">
         <v>448400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>481900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>168900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>352200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3978500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-885100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-516500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-929600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>773400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>517000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>367200</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>585500</v>
+      </c>
+      <c r="E83" s="3">
         <v>428600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>301300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>146900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>110200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>374100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>440200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>486500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>548000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>611100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>634300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>879400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>758600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>658600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>951700</v>
+      </c>
+      <c r="E89" s="3">
         <v>655500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>574300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>281000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>273200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>186800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>171900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>416700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1142700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1764900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P89" s="3">
         <v>1702300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1381700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>740200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-519500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-575300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-409600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-174300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-169000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-148900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-268800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-194800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-120700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-711400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-422500</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-2487500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1669800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2621200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-350100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-959000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-366500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>375800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>193400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-121500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-256000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-189400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-118300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-686600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-432500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-2485100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1790900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2521500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,20 +4688,21 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>320400</v>
+      </c>
+      <c r="E96" s="3">
         <v>277800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>98800</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -4486,26 +4719,29 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-47500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-315500</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-194900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-138300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-150500</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,57 +4889,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-373900</v>
+      </c>
+      <c r="E100" s="3">
         <v>188100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-325800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-367800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-367900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>107400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-269400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-361200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-242700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-888600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>615200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>452100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1682600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4725,8 +4973,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4743,55 +4991,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>227700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-115500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-118000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>289000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-168300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>259100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-270000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-286900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-62900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>213500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>443700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P102" s="3">
         <v>-167600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>42900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-98700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
